--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5493-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5493-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1304B602-7177-4690-9A33-C59A16A768E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{332D1313-7727-4ABC-A3F7-B1E0C0AC8125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{62AA979B-14DB-40C7-A4C6-8FDEC124863D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{80BFF9E1-A5F2-40E5-BCD6-D392E5AEE36A}"/>
   </bookViews>
   <sheets>
     <sheet name="5493-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1538,28 +1538,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{435CE65D-E9D6-46EA-A048-CAA37CA13A6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D3FC79F-D43A-4139-A122-17422928D162}">
   <dimension ref="A1:X49"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1749,7 +1749,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2024</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2023</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2022</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2021</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>7.45</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>7.45</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2020</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2019</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2018</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2017</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>6.26</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2016</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2015</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2014</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>2013</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>9.23</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2012</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>2011</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>2010</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>2009</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>2008</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>2007</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>2006</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>2005</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>2004</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>2003</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>2002</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>2001</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>2000</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="36">
         <v>1999</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>1998</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="36">
         <v>1997</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38" t="s">
         <v>66</v>
       </c>
